--- a/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The one big figure" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="The one big figure" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'The one big figure'!$A$5:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'The one big figure'!$A$5:$K$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -87,12 +87,12 @@
     </font>
     <font>
       <name val="Segoe UI Semibold"/>
-      <color rgb="004D7E83"/>
+      <color rgb="00648ECA"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI Semibold"/>
-      <color rgb="00648ECA"/>
+      <color rgb="004D7E83"/>
       <sz val="9"/>
     </font>
     <font>
@@ -161,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,40 +215,43 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -338,13 +341,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1100" b="0">
                 <a:solidFill>
@@ -379,17 +382,17 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A530B8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -398,10 +401,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B04545"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -410,10 +413,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3A6165"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -422,10 +425,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3A6165"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -434,10 +437,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3A6165"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -446,562 +449,598 @@
           <dPt>
             <idx val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="3A6165"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="B04545"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="6"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4D7E83"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="28"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="29"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="30"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="31"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="32"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="33"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="34"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="35"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="36"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="37"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="38"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="39"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="40"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="41"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="42"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="43"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="44"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="45"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="46"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="47"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="3A6165"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="48"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="00928F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="8"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="9"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="10"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="11"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="12"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="49"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="B487C7"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="13"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="14"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="15"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="A530B8"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="16"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="17"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="18"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4D7E83"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="19"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="20"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="21"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="22"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="23"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="24"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="25"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="26"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="27"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="28"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="29"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="30"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="31"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="32"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="33"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="A530B8"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="34"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="50"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="B487C7"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="35"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="36"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="37"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="38"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="A530B8"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="39"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="51"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3A6165"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="52"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3A6165"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="53"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="B487C7"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="40"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="54"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="B487C7"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="41"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="42"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="43"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="44"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3A6165"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="45"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="46"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="47"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="48"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="49"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3A6165"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="50"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3A6165"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="51"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1009,12 +1048,12 @@
           </dPt>
           <cat>
             <strRef>
-              <f>'The one big figure'!$B$6:$B$57</f>
+              <f>'The one big figure'!$B$6:$B$60</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'The one big figure'!$J$6:$J$57</f>
+              <f>'The one big figure'!$J$6:$J$60</f>
             </numRef>
           </val>
         </ser>
@@ -1032,8 +1071,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1049,7 +1088,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -1057,8 +1096,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -1092,7 +1131,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -1100,8 +1139,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -1128,7 +1167,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1137,13 +1176,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1100" b="0">
                 <a:solidFill>
@@ -1174,26 +1213,26 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'The one big figure'!C63</f>
+              <f>'The one big figure'!C66</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4D7E83"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <strRef>
-              <f>'The one big figure'!$B$64:$B$72</f>
+              <f>'The one big figure'!$B$67:$B$75</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'The one big figure'!$C$64:$C$72</f>
+              <f>'The one big figure'!$C$67:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -1202,26 +1241,26 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'The one big figure'!D63</f>
+              <f>'The one big figure'!D66</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="D8E7E8"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <strRef>
-              <f>'The one big figure'!$B$64:$B$72</f>
+              <f>'The one big figure'!$B$67:$B$75</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'The one big figure'!$D$64:$D$72</f>
+              <f>'The one big figure'!$D$67:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -1241,7 +1280,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -1249,8 +1288,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -1283,8 +1322,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1299,7 +1338,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="B9CFD1"/>
             </a:solidFill>
@@ -1307,8 +1346,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800">
                 <a:solidFill>
@@ -1335,8 +1374,8 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="800">
               <a:solidFill>
@@ -1361,7 +1400,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1370,7 +1409,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>12</col>
@@ -1378,16 +1417,16 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="21096000"/>
+    <ext cx="9360000" cy="22230000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1397,7 +1436,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="3240000"/>
@@ -1407,9 +1446,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1708,7 +1747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1734,7 +1773,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>52 of the 97 progress indicators have gained data since the report. They are measured in Mt, TWh, %, vehicles and head of cattle, so they are shown as the change against each indicator's own report baseline — the figure answers “how far, and which way”, not “how big”. The numbers behind every bar are in the table below it.</t>
+          <t>55 of the 97 progress indicators have gained data since the report. They are measured in Mt, TWh, %, vehicles and head of cattle, so they are shown as the change against each indicator's own report baseline — the figure answers “how far, and which way”, not “how big”. The numbers behind every bar are in the table below it.</t>
         </is>
       </c>
     </row>
@@ -2028,194 +2067,194 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>I2 (steel, production)</t>
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>E6</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Steel production (EU)</t>
+          <t>Energy-related methane emissions (EU-27)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Energy supply</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E11" s="13" t="n">
         <v>2021</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>152.8</v>
+        <v>69.91</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>126.2</v>
+        <v>57.77</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>-26.60000000000001</v>
+        <v>-12.13999999999999</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.1740837696335079</v>
+        <v>-0.1736518380775282</v>
       </c>
       <c r="K11" s="16" t="inlineStr">
         <is>
-          <t>2–5% off source</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>E6</t>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>B5b</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Energy-related methane emissions (EU-27)</t>
+          <t>Fossil share of tertiary energy mix</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Energy supply</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>69.91</v>
+        <v>38.74</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>57.77</v>
+        <v>32.2</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>-12.13999999999999</v>
+        <v>-6.539999999999999</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.1736518380775282</v>
+        <v>-0.1688177594217862</v>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>B2</t>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>I2 (steel, production)</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Final energy consumption in buildings</t>
+          <t>Steel production (EU)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>TWh</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E13" s="13" t="n">
         <v>2021</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4878.7</v>
+        <v>152.8</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>4037.9</v>
+        <v>128.8</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>-840.7999999999997</v>
+        <v>-24</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.1723409924775042</v>
+        <v>-0.1570680628272251</v>
       </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>2–5% off source</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>B5b</t>
+          <t>I2 (cement, production)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Fossil share of tertiary energy mix</t>
+          <t>Cement production (EU)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>38.74</v>
+        <v>182.5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>32.2</v>
+        <v>157.7</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>-6.539999999999999</v>
+        <v>-24.80000000000001</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.1688177594217862</v>
+        <v>-0.1358904109589042</v>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>I2 (cement, production)</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Cement production (EU)</t>
+          <t>Industrial GHG emissions</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -2225,26 +2264,26 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>182.5</v>
+        <v>691.3</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>159.1</v>
+        <v>611.4</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>-23.40000000000001</v>
+        <v>-79.89999999999998</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.1282191780821918</v>
+        <v>-0.1155793432663098</v>
       </c>
       <c r="K15" s="16" t="inlineStr">
         <is>
@@ -2253,187 +2292,187 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>I1</t>
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>B2</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Industrial GHG emissions</t>
+          <t>Final energy consumption in buildings</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>4878.7</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>4324.2</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>-554.5</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>-0.1136573267468793</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Average CO₂ intensity of new passenger cars (WLTP)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>g CO₂/km</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>-0.1062846580406654</v>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Residential + tertiary building GHG emissions</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
           <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>691.3</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>611.4</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>-79.89999999999998</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>-0.1155793432663098</v>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>I5</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Industrial final energy consumption (EU)</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>TWh</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>2795.2</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>2497.2</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>-298</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>-0.1066113337149399</v>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Average CO₂ intensity of new passenger cars (WLTP)</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>g CO₂/km</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>108.2</v>
+        <v>481.8</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>96.7</v>
+        <v>430.7</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>-11.5</v>
+        <v>-51.10000000000002</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.1062846580406654</v>
+        <v>-0.1060606060606061</v>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Industrial final energy consumption (EU)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2795.2</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>2501.3</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>-293.8999999999996</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>-0.1051445334859758</v>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
           <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Residential + tertiary building GHG emissions</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Buildings</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>481.8</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>-51.10000000000002</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>-0.1060606060606061</v>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>A4 (pig, herd)</t>
         </is>
@@ -2478,268 +2517,268 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Gross inland energy consumption (EU-27)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Energy demand</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>16534</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>15023.9</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>-1510.1</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>-0.09133301076569494</v>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>EU fossil-fuel subsidies (FFST)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Finance &amp; innovation</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>billion EUR</t>
         </is>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E22" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F22" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G22" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H22" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="I22" s="8" t="n">
         <v>-11</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J22" s="9" t="n">
         <v>-0.09016393442622951</v>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>O2 (PEC)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Primary energy consumption (EU-27)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Energy demand</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>15248</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>13883</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>-1365</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>-0.0895199370409234</v>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>A2 (bovine, production)</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Bovine meat: production (EU)</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Mt</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E24" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F24" s="8" t="n">
         <v>6.936</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G24" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H24" s="8" t="n">
         <v>6.32</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I24" s="8" t="n">
         <v>-0.6159999999999997</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J24" s="9" t="n">
         <v>-0.08881199538638979</v>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Reproduces from source</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>A4 (bovine, production)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Bovine meat: production (EU)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Mt</t>
         </is>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E25" s="13" t="n">
         <v>2020</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F25" s="14" t="n">
         <v>6.936</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H25" s="14" t="n">
         <v>6.32</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="I25" s="14" t="n">
         <v>-0.6159999999999997</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J25" s="15" t="n">
         <v>-0.08881199538638979</v>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K25" s="16" t="inlineStr">
         <is>
           <t>Reproduces from source</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>O1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Total EU GHG emissions (European Climate Law scope)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Emissions</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Mt CO₂eq</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E26" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F26" s="8" t="n">
         <v>3333.9</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>3043.2</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>-290.7000000000003</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>-0.08719517681994068</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>A2 (pig, GHG)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Pig meat: GHG emissions (EU)</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>-2.399999999999999</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>-0.08397480755773264</v>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>O2 (PEC)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Primary energy consumption (EU-27)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Energy demand</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>TWh</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>15248</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>13979.3</v>
+        <v>3043.2</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>-1268.700000000001</v>
+        <v>-290.7000000000003</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.08320435466946491</v>
+        <v>-0.08719517681994068</v>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
@@ -2748,142 +2787,142 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>B5a</t>
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>A2 (pig, GHG)</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Fossil share of residential energy mix</t>
+          <t>Pig meat: GHG emissions (EU)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E27" s="13" t="n">
         <v>2021</v>
       </c>
       <c r="F27" s="14" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>-0.08397480755773264</v>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>B5a</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Fossil share of residential energy mix</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>45.58</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G28" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H28" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I28" s="8" t="n">
         <v>-3.579999999999998</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J28" s="9" t="n">
         <v>-0.07854322071083805</v>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>A4 (dairy, herd)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Dairy products: herd size (EU)</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>million heads</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E29" s="13" t="n">
         <v>2020</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F29" s="14" t="n">
         <v>20.63</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G29" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H29" s="14" t="n">
         <v>19.02</v>
       </c>
-      <c r="I28" s="8" t="n">
+      <c r="I29" s="14" t="n">
         <v>-1.609999999999999</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J29" s="15" t="n">
         <v>-0.07804168686379057</v>
       </c>
-      <c r="K28" s="10" t="inlineStr">
+      <c r="K29" s="16" t="inlineStr">
         <is>
           <t>Reproduces from source</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>L8</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Total bioenergy use (EU-27)</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>LULUCF</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>TWh</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>1795.7</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>1663.5</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>-132.2</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>-0.07362031519741608</v>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>O2 (FEC)</t>
         </is>
@@ -2913,13 +2952,13 @@
         <v>2024</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>10467</v>
+        <v>10471.8</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>-796</v>
+        <v>-791.2000000000007</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.07067388795170025</v>
+        <v>-0.0702477137529966</v>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
@@ -2928,7 +2967,7 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>A4 (bovine, herd)</t>
         </is>
@@ -2973,7 +3012,7 @@
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>A2 (pig, production)</t>
         </is>
@@ -3018,7 +3057,7 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>A4 (pig, production)</t>
         </is>
@@ -3065,50 +3104,50 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>O3</t>
+          <t>T3a</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Gross inland energy consumption (EU-27)</t>
+          <t>Road share of motorised inland passenger transport</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Energy demand</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>16534</v>
+        <v>86.5</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>15575.3</v>
+        <v>83.3</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>-958.7000000000007</v>
+        <v>-3.200000000000003</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.05798354905044156</v>
+        <v>-0.03699421965317922</v>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>A2 (pig, intensity)</t>
         </is>
@@ -3153,52 +3192,52 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>I6</t>
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Electricity share of industrial final energy use</t>
+          <t>Total bioenergy use (EU-27)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>LULUCF</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>TWh</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>33.22</v>
+        <v>1795.7</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>32.6</v>
+        <v>1761.2</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>-0.6199999999999974</v>
+        <v>-34.5</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.01866345574954839</v>
+        <v>-0.01921256334577045</v>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>2–5% off source</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>A6</t>
         </is>
@@ -3243,7 +3282,7 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -3288,7 +3327,7 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
@@ -3333,7 +3372,7 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>T6a</t>
         </is>
@@ -3378,7 +3417,7 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>A2 (dairy, production)</t>
         </is>
@@ -3423,7 +3462,7 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>A4 (dairy, production)</t>
         </is>
@@ -3468,7 +3507,7 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>B4 (population)</t>
         </is>
@@ -3513,88 +3552,88 @@
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>F2 (share)</t>
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Green share of EU bond issuance</t>
+          <t>Transport GHG emissions (EU)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Finance &amp; innovation</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>6.74</v>
+        <v>906.6</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>6.9</v>
+        <v>920</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.1600000000000001</v>
+        <v>13.39999999999998</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.02373887240356085</v>
+        <v>0.01478049856607101</v>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>T2b</t>
+          <t>F2 (share)</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Total freight transport demand</t>
+          <t>Green share of EU bond issuance</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Finance &amp; innovation</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Gtkm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E45" s="13" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>2254</v>
+        <v>6.74</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>2319</v>
+        <v>6.9</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>65</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0.02883762200532387</v>
+        <v>0.02373887240356085</v>
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
@@ -3603,178 +3642,178 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>I6</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Transport GHG emissions (EU)</t>
+          <t>Electricity share of industrial final energy use</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>906.6</v>
+        <v>33.22</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>934.7</v>
+        <v>34.02</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>28.10000000000002</v>
+        <v>0.8000000000000043</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.03099492609750719</v>
+        <v>0.02408187838651428</v>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>2–5% off source</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>I3</t>
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>T2b</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Circular material use rate (EU)</t>
+          <t>Total freight transport demand</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
+          <t>Gtkm</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>2254</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>2319</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="J47" s="15" t="n">
+        <v>0.02883762200532387</v>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Electrification rate of final energy use</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Energy demand</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E48" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="F47" s="14" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H47" s="14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J47" s="15" t="n">
-        <v>0.04273504273504274</v>
-      </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>LULUCF net GHG balance</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>LULUCF</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>2022</v>
-      </c>
       <c r="F48" s="8" t="n">
-        <v>-244</v>
+        <v>22.75</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>-231</v>
+        <v>23.44</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>13</v>
+        <v>0.6900000000000013</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.05327868852459016</v>
+        <v>0.03032967032967039</v>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>L6</t>
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>I3</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Forest land living-biomass carbon sink</t>
+          <t>Circular material use rate (EU)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>LULUCF</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
         <v>2021</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>231.8</v>
+        <v>11.7</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>258.3</v>
+        <v>12.2</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>26.5</v>
+        <v>0.5</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0.1143226919758412</v>
+        <v>0.04273504273504274</v>
       </c>
       <c r="K49" s="16" t="inlineStr">
         <is>
@@ -3783,59 +3822,59 @@
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>E2 (RES)</t>
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>L1</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Non-biomass renewable share of EU electricity mix</t>
+          <t>LULUCF net GHG balance</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Energy supply</t>
+          <t>LULUCF</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>33.76</v>
+        <v>-244</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>41.38</v>
+        <v>-231</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>7.620000000000005</v>
+        <v>13</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.2257109004739338</v>
+        <v>0.05327868852459016</v>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>2–5% off source</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
-        <is>
-          <t>L7</t>
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>L6</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Non-forest LULUCF net GHG emissions</t>
+          <t>Forest land living-biomass carbon sink</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -3852,19 +3891,19 @@
         <v>2021</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>97.44</v>
+        <v>231.8</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>123</v>
+        <v>258.3</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>25.56</v>
+        <v>26.5</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0.2623152709359606</v>
+        <v>0.1143226919758412</v>
       </c>
       <c r="K51" s="16" t="inlineStr">
         <is>
@@ -3873,64 +3912,64 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>B6</t>
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>L7</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>EU stock of installed heat pumps</t>
+          <t>Non-forest LULUCF net GHG emissions</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>LULUCF</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>million units</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>19.79</v>
+        <v>97.44</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>25.5</v>
+        <v>123</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>5.710000000000001</v>
+        <v>25.56</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.2885295603840324</v>
+        <v>0.2623152709359606</v>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
-        <is>
-          <t>T5a</t>
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>E2 (RES)</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>ZEV share of new passenger car registrations</t>
+          <t>Non-biomass renewable share of EU electricity mix</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Energy supply</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3942,109 +3981,109 @@
         <v>2022</v>
       </c>
       <c r="F53" s="14" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>9.450000000000003</v>
+      </c>
+      <c r="J53" s="15" t="n">
+        <v>0.2799170616113745</v>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>2–5% off source</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>EU stock of installed heat pumps</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>million units</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>5.710000000000001</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.2885295603840324</v>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>T5a</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>ZEV share of new passenger car registrations</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F55" s="14" t="n">
         <v>13.41</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H53" s="14" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>3.989999999999998</v>
-      </c>
-      <c r="J53" s="15" t="n">
-        <v>0.2975391498881431</v>
-      </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>T2a</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Total passenger transport demand</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Gpkm</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>4435.8</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H54" s="8" t="n">
-        <v>5932</v>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>1496.2</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>0.3373010505433067</v>
-      </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
-        <is>
-          <t>E4b/c</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>Annual wind capacity additions (EU)</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>Energy supply</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>GW/yr</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>10.72</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>15.1</v>
+        <v>17.4</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>4.379999999999999</v>
+        <v>3.989999999999998</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>0.4085820895522387</v>
+        <v>0.2975391498881431</v>
       </c>
       <c r="K55" s="16" t="inlineStr">
         <is>
@@ -4053,274 +4092,409 @@
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>T2a</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Total passenger transport demand</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Gpkm</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>4435.8</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>5932</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>1496.2</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.3373010505433067</v>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>E4b/c</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Annual wind capacity additions (EU)</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Energy supply</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>GW/yr</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J57" s="15" t="n">
+        <v>0.4291044776119403</v>
+      </c>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>E4a</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Annual solar PV capacity additions (EU)</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Energy supply</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>GW/yr</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E58" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F58" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G56" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>39.39999999999999</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>1.533073929961089</v>
-      </c>
-      <c r="K56" s="10" t="inlineStr">
+      <c r="G58" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>35.26000000000001</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>1.371984435797665</v>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="29" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>T5b</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Zero-emission lorries in the EU fleet</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>3794</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>9831</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>6037</v>
+      </c>
+      <c r="J59" s="15" t="n">
+        <v>1.591196626251977</v>
+      </c>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>T3b</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Intra-EU air passenger transport</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Gpkm</t>
         </is>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E60" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="F57" s="14" t="n">
+      <c r="F60" s="8" t="n">
         <v>177.9</v>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="G60" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="H57" s="14" t="n">
+      <c r="H60" s="8" t="n">
         <v>582</v>
       </c>
-      <c r="I57" s="14" t="n">
+      <c r="I60" s="8" t="n">
         <v>404.1</v>
       </c>
-      <c r="J57" s="15" t="n">
+      <c r="J60" s="9" t="n">
         <v>2.27150084317032</v>
       </c>
-      <c r="K57" s="16" t="inlineStr">
+      <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="31" t="inlineStr">
-        <is>
-          <t>Notes: bars are coloured by report chapter. A long bar is a large move relative to that indicator's own baseline, not a large quantity — indicators with small baselines (capacity additions, ZEV shares) move by large percentages by nature.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>Source: ESABCC (2024) “Towards EU climate neutrality”, progress indicators, extended with the post-publication points in the Policy Gap 2.0 indicator database. Every post-report value was re-checked against its primary source on 27 July 2026 (see the “Source check” column).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="32" t="inlineStr">
         <is>
+          <t>Notes: bars are coloured by report chapter. A long bar is a large move relative to that indicator's own baseline, not a large quantity — indicators with small baselines (capacity additions, ZEV shares) move by large percentages by nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>Source: ESABCC (2024) “Towards EU climate neutrality”, progress indicators, extended with the post-publication points in the Policy Gap 2.0 indicator database. Every post-report value was re-checked against its primary source on 27 July 2026 (see the “Source check” column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
           <t>Coverage — how much of each chapter has new data</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Chapter</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>With new data</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Still at the report figure</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="6" t="inlineStr"/>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Emissions</t>
         </is>
       </c>
-      <c r="C64" s="33" t="n">
+      <c r="C67" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="33" t="n">
+      <c r="D67" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="12" t="inlineStr"/>
-      <c r="B65" s="12" t="inlineStr">
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="12" t="inlineStr"/>
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>Energy supply</t>
         </is>
       </c>
-      <c r="C65" s="34" t="n">
+      <c r="C68" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="D65" s="34" t="n">
+      <c r="D68" s="35" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="6" t="inlineStr"/>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="6" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Energy demand</t>
         </is>
       </c>
-      <c r="C66" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D66" s="33" t="n">
+      <c r="C69" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="12" t="inlineStr"/>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="C70" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" s="35" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="6" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C71" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="D71" s="34" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="12" t="inlineStr"/>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="C67" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="D67" s="34" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="C68" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="D68" s="33" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="12" t="inlineStr"/>
-      <c r="B69" s="12" t="inlineStr">
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="12" t="inlineStr"/>
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>Buildings</t>
         </is>
       </c>
-      <c r="C69" s="34" t="n">
+      <c r="C72" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="D69" s="34" t="n">
+      <c r="D72" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="6" t="inlineStr"/>
-      <c r="B70" s="6" t="inlineStr">
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="6" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C70" s="33" t="n">
+      <c r="C73" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="D70" s="33" t="n">
+      <c r="D73" s="34" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="12" t="inlineStr"/>
-      <c r="B71" s="12" t="inlineStr">
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="12" t="inlineStr"/>
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>LULUCF</t>
         </is>
       </c>
-      <c r="C71" s="34" t="n">
+      <c r="C74" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="D71" s="34" t="n">
+      <c r="D74" s="35" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="6" t="inlineStr"/>
-      <c r="B72" s="6" t="inlineStr">
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="6" t="inlineStr"/>
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Finance &amp; innovation</t>
         </is>
       </c>
-      <c r="C72" s="33" t="n">
+      <c r="C75" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D72" s="33" t="n">
+      <c r="D75" s="34" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K57"/>
+  <autoFilter ref="A5:K60"/>
   <mergeCells count="5">
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
@@ -4354,13 +4354,6 @@
           <t>Still at the report figure</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="6" t="inlineStr"/>

--- a/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
@@ -10,7 +10,7 @@
     <sheet name="The one big figure" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'The one big figure'!$A$5:$K$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'The one big figure'!$A$5:$K$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,12 +62,12 @@
     </font>
     <font>
       <name val="Segoe UI Semibold"/>
-      <color rgb="00B04545"/>
+      <color rgb="003A6165"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI Semibold"/>
-      <color rgb="003A6165"/>
+      <color rgb="00B04545"/>
       <sz val="9"/>
     </font>
     <font>
@@ -191,7 +191,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,28 +209,37 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,19 +248,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -402,6 +402,54 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3A6165"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3A6165"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3A6165"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
                 <a:srgbClr val="B04545"/>
               </a:solidFill>
               <a:ln>
@@ -411,7 +459,31 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="2"/>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="3A6165"/>
@@ -423,7 +495,715 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="3"/>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4D7E83"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="28"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="29"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="30"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="31"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="32"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="33"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="34"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="35"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="36"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="37"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="38"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="39"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="40"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="41"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="42"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="43"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="44"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="45"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="46"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="47"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="48"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="49"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="50"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="51"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="52"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="53"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="54"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="55"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A530B8"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="56"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="57"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="58"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="59"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="648ECA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="60"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="61"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="62"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="6E8B1F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="63"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="64"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="65"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="66"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="67"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="007B6C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="68"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="3A6165"/>
@@ -435,7 +1215,55 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="4"/>
+            <idx val="69"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00928F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="70"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="71"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B487C7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="72"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="73"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="3A6165"/>
@@ -447,7 +1275,19 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="5"/>
+            <idx val="74"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B04545"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="75"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="3A6165"/>
@@ -459,67 +1299,7 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="6"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="8"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="9"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="10"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="11"/>
+            <idx val="76"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="B487C7"/>
@@ -531,511 +1311,7 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="12"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="13"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="14"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="15"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="16"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A530B8"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="17"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="18"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="19"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="20"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="4D7E83"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="21"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="22"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="23"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="24"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="25"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="26"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="27"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="28"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="29"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="30"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="31"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="32"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="33"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A530B8"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="34"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="35"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="36"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="6E8B1F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="37"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="38"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="39"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A530B8"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="40"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="41"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="42"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="648ECA"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="43"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B04545"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="44"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="45"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="46"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="007B6C"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="47"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="3A6165"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="48"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00928F"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="49"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="50"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="51"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="3A6165"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="52"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="3A6165"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="53"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="B487C7"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="54"/>
+            <idx val="77"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="B487C7"/>
@@ -1048,12 +1324,12 @@
           </dPt>
           <cat>
             <strRef>
-              <f>'The one big figure'!$B$6:$B$60</f>
+              <f>'The one big figure'!$B$6:$B$83</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'The one big figure'!$J$6:$J$60</f>
+              <f>'The one big figure'!$J$6:$J$83</f>
             </numRef>
           </val>
         </ser>
@@ -1213,7 +1489,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'The one big figure'!C66</f>
+              <f>'The one big figure'!C89</f>
             </strRef>
           </tx>
           <spPr>
@@ -1227,12 +1503,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'The one big figure'!$B$67:$B$75</f>
+              <f>'The one big figure'!$B$90:$B$98</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'The one big figure'!$C$67:$C$75</f>
+              <f>'The one big figure'!$C$90:$C$98</f>
             </numRef>
           </val>
         </ser>
@@ -1241,7 +1517,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'The one big figure'!D66</f>
+              <f>'The one big figure'!D89</f>
             </strRef>
           </tx>
           <spPr>
@@ -1255,12 +1531,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'The one big figure'!$B$67:$B$75</f>
+              <f>'The one big figure'!$B$90:$B$98</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'The one big figure'!$D$67:$D$75</f>
+              <f>'The one big figure'!$D$90:$D$98</f>
             </numRef>
           </val>
         </ser>
@@ -1417,7 +1693,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="22230000"/>
+    <ext cx="9360000" cy="30924000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1436,7 +1712,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="3240000"/>
@@ -1747,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1773,7 +2049,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>55 of the 97 progress indicators have gained data since the report. They are measured in Mt, TWh, %, vehicles and head of cattle, so they are shown as the change against each indicator's own report baseline — the figure answers “how far, and which way”, not “how big”. The numbers behind every bar are in the table below it.</t>
+          <t>78 of the 97 progress indicators have gained data since the report. They are measured in Mt, TWh, %, vehicles and head of cattle, so they are shown as the change against each indicator's own report baseline — the figure answers “how far, and which way”, not “how big”. The numbers behind every bar are in the table below it.</t>
         </is>
       </c>
     </row>
@@ -1844,12 +2120,12 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Cleantech venture &amp; growth investment in the EU</t>
+          <t>Climate-related share of EU patent filings</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1859,75 +2135,75 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>% of GDP</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.06</v>
+        <v>11.94</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.04</v>
+        <v>6.75</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>-0.02</v>
+        <v>-5.19</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4346733668341709</v>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>I2 (chemicals, production)</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Chemicals production (EU)</t>
+          <t>Cleantech venture &amp; growth investment in the EU</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Finance &amp; innovation</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>% of GDP</t>
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>26.84</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>18.55</v>
+        <v>0.04</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>-8.289999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>-0.3088673621460507</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
@@ -2067,104 +2343,104 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>E6</t>
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>I2 (chemicals, use)</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Energy-related methane emissions (EU-27)</t>
+          <t>Chemicals apparent use (consumption) (EU)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Energy supply</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>69.91</v>
+        <v>29.11</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>57.77</v>
+        <v>22.95</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>-12.13999999999999</v>
+        <v>-6.16</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-0.1736518380775282</v>
+        <v>-0.211611130195809</v>
       </c>
       <c r="K11" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>B5b</t>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>I2 (steel, trade)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Fossil share of tertiary energy mix</t>
+          <t>Steel net trade balance (EU)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>38.74</v>
+        <v>-25.77</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>32.2</v>
+        <v>-30.891</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>-6.539999999999999</v>
+        <v>-5.120999999999999</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.1688177594217862</v>
+        <v>-0.1987194412107101</v>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>I2 (steel, production)</t>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>I2 (chemicals, production)</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Steel production (EU)</t>
+          <t>Chemicals production (EU)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -2178,128 +2454,128 @@
         </is>
       </c>
       <c r="E13" s="13" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>152.8</v>
+        <v>26.84</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>128.8</v>
+        <v>21.59</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>-24</v>
+        <v>-5.25</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-0.1570680628272251</v>
+        <v>-0.1956035767511178</v>
       </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
-          <t>2–5% off source</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>I2 (cement, production)</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>E6</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Cement production (EU)</t>
+          <t>Energy-related methane emissions (EU-27)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Energy supply</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>182.5</v>
+        <v>69.91</v>
       </c>
       <c r="G14" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>-12.13999999999999</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>-0.1736518380775282</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>I2 (steel, production)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Steel production (EU)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="G15" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="H14" s="8" t="n">
-        <v>157.7</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>-24.80000000000001</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>-0.1358904109589042</v>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Industrial GHG emissions</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>691.3</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>2024</v>
-      </c>
       <c r="H15" s="14" t="n">
-        <v>611.4</v>
+        <v>128.8</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>-79.89999999999998</v>
+        <v>-24</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-0.1155793432663098</v>
+        <v>-0.1570680628272251</v>
       </c>
       <c r="K15" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>2–5% off source</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>B2</t>
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>B5b</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Final energy consumption in buildings</t>
+          <t>Fossil share of tertiary energy mix</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -2309,26 +2585,26 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>4878.7</v>
+        <v>38.74</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4324.2</v>
+        <v>32.85</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>-554.5</v>
+        <v>-5.890000000000001</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.1136573267468793</v>
+        <v>-0.1520392359318534</v>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
@@ -2337,178 +2613,178 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>I2 (cement, production)</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Average CO₂ intensity of new passenger cars (WLTP)</t>
+          <t>Cement production (EU)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>g CO₂/km</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>108.2</v>
+        <v>182.5</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>96.7</v>
+        <v>157.7</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>-11.5</v>
+        <v>-24.80000000000001</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-0.1062846580406654</v>
+        <v>-0.1358904109589042</v>
       </c>
       <c r="K17" s="16" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>B1</t>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>I2 (cement, use)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Residential + tertiary building GHG emissions</t>
+          <t>Cement apparent use (consumption) (EU)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>481.8</v>
+        <v>170.5</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>430.7</v>
+        <v>148.1</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>-51.10000000000002</v>
+        <v>-22.40000000000001</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.1060606060606061</v>
+        <v>-0.1313782991202346</v>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>I5</t>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>T6b</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Industrial final energy consumption (EU)</t>
+          <t>Use of first-generation (food-crop) biofuels in transport</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>-15.19999999999999</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>-0.1287044877222692</v>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Industrial GHG emissions</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>TWh</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>2795.2</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>2501.3</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>-293.8999999999996</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>-0.1051445334859758</v>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>A4 (pig, herd)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Pig meat: herd size (EU)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>million heads</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>140</v>
+        <v>691.3</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>126.1</v>
+        <v>611.4</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>-13.90000000000001</v>
+        <v>-79.89999999999998</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.09928571428571432</v>
+        <v>-0.1155793432663098</v>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
@@ -2519,17 +2795,17 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>O3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Gross inland energy consumption (EU-27)</t>
+          <t>Final energy consumption in buildings</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Energy demand</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -2541,19 +2817,19 @@
         <v>2021</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>16534</v>
+        <v>4878.7</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>15023.9</v>
+        <v>4326.8</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>-1510.1</v>
+        <v>-551.8999999999996</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>-0.09133301076569494</v>
+        <v>-0.1131243978928812</v>
       </c>
       <c r="K21" s="16" t="inlineStr">
         <is>
@@ -2562,43 +2838,43 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>F1</t>
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>EU fossil-fuel subsidies (FFST)</t>
+          <t>Average CO₂ intensity of new passenger cars (WLTP)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Finance &amp; innovation</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>billion EUR</t>
+          <t>g CO₂/km</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>122</v>
+        <v>108.2</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>111</v>
+        <v>96.7</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>-11</v>
+        <v>-11.5</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.09016393442622951</v>
+        <v>-0.1062846580406654</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -2609,41 +2885,41 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>O2 (PEC)</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Primary energy consumption (EU-27)</t>
+          <t>Residential + tertiary building GHG emissions</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Energy demand</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>TWh</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>15248</v>
+        <v>481.8</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>13883</v>
+        <v>430.7</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>-1365</v>
+        <v>-51.10000000000002</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>-0.0895199370409234</v>
+        <v>-0.1060606060606061</v>
       </c>
       <c r="K23" s="16" t="inlineStr">
         <is>
@@ -2652,88 +2928,88 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>A2 (bovine, production)</t>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>I5</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bovine meat: production (EU)</t>
+          <t>Industrial final energy consumption (EU)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>2795.2</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>2506.3</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>-288.8999999999996</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>-0.1033557527189466</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>A4 (pig, herd)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Pig meat: herd size (EU)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>6.936</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>-0.6159999999999997</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>-0.08881199538638979</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>A4 (bovine, production)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Bovine meat: production (EU)</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>million heads</t>
         </is>
       </c>
       <c r="E25" s="13" t="n">
         <v>2020</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>6.936</v>
+        <v>140</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>6.32</v>
+        <v>126.1</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>-0.6159999999999997</v>
+        <v>-13.90000000000001</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>-0.08881199538638979</v>
+        <v>-0.09928571428571432</v>
       </c>
       <c r="K25" s="16" t="inlineStr">
         <is>
@@ -2742,133 +3018,133 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>O1</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>I2 (steel, use)</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Total EU GHG emissions (European Climate Law scope)</t>
+          <t>Steel apparent use (consumption) (EU)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>3333.9</v>
+        <v>149</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>3043.2</v>
+        <v>134.4</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>-290.7000000000003</v>
+        <v>-14.59999999999999</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.08719517681994068</v>
+        <v>-0.09798657718120801</v>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>A2 (pig, GHG)</t>
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>O3</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Pig meat: GHG emissions (EU)</t>
+          <t>Gross inland energy consumption (EU-27)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Energy demand</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>TWh</t>
         </is>
       </c>
       <c r="E27" s="13" t="n">
         <v>2021</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>28.58</v>
+        <v>16534</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>26.18</v>
+        <v>15023.9</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>-2.399999999999999</v>
+        <v>-1510.1</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>-0.08397480755773264</v>
+        <v>-0.09133301076569494</v>
       </c>
       <c r="K27" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>B5a</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Fossil share of residential energy mix</t>
+          <t>EU fossil-fuel subsidies (FFST)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Finance &amp; innovation</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>billion EUR</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>45.58</v>
+        <v>122</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>-3.579999999999998</v>
+        <v>-11</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.07854322071083805</v>
+        <v>-0.09016393442622951</v>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
@@ -2877,104 +3153,104 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>A4 (dairy, herd)</t>
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>O2 (PEC)</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Dairy products: herd size (EU)</t>
+          <t>Primary energy consumption (EU-27)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
+          <t>Energy demand</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>TWh</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>15248</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>13883</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>-1365</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>-0.0895199370409234</v>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>A2 (bovine, production)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Bovine meat: production (EU)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>million heads</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="n">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="F29" s="14" t="n">
-        <v>20.63</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="F30" s="8" t="n">
+        <v>6.936</v>
+      </c>
+      <c r="G30" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>-1.609999999999999</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>-0.07804168686379057</v>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
+      <c r="H30" s="8" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>-0.6159999999999997</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>-0.08881199538638979</v>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>Reproduces from source</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>O2 (FEC)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Final energy consumption (EU-27)</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Energy demand</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TWh</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>11263</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>10471.8</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>-791.2000000000007</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>-0.0702477137529966</v>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>A4 (bovine, herd)</t>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>A4 (bovine, production)</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Bovine meat: herd size (EU)</t>
+          <t>Bovine meat: production (EU)</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -2984,26 +3260,26 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>million heads</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E31" s="13" t="n">
         <v>2020</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>60.16</v>
+        <v>6.936</v>
       </c>
       <c r="G31" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>56.26</v>
+        <v>6.32</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>-3.899999999999999</v>
+        <v>-0.6159999999999997</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>-0.06482712765957445</v>
+        <v>-0.08881199538638979</v>
       </c>
       <c r="K31" s="16" t="inlineStr">
         <is>
@@ -3012,43 +3288,43 @@
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>A2 (pig, production)</t>
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>O1</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Pig meat: production (EU)</t>
+          <t>Total EU GHG emissions (European Climate Law scope)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Emissions</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>23.22</v>
+        <v>3333.9</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>21.84</v>
+        <v>3043.2</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>-1.379999999999999</v>
+        <v>-290.7000000000003</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.05943152454780358</v>
+        <v>-0.08719517681994068</v>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
@@ -3057,104 +3333,104 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>A4 (pig, production)</t>
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>B5a</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Pig meat: production (EU)</t>
+          <t>Fossil share of residential energy mix</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>23.22</v>
+        <v>45.58</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>21.84</v>
+        <v>41.74</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>-1.379999999999999</v>
+        <v>-3.839999999999996</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>-0.05943152454780358</v>
+        <v>-0.08424747696358043</v>
       </c>
       <c r="K33" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>T3a</t>
+          <t>A2 (pig, GHG)</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Road share of motorised inland passenger transport</t>
+          <t>Pig meat: GHG emissions (EU)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>86.5</v>
+        <v>28.58</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>83.3</v>
+        <v>26.18</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>-3.200000000000003</v>
+        <v>-2.399999999999999</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.03699421965317922</v>
+        <v>-0.08397480755773264</v>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>A2 (pig, intensity)</t>
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>A4 (dairy, herd)</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Pig meat: GHG intensity (EU)</t>
+          <t>Dairy products: herd size (EU)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -3164,26 +3440,26 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>t CO₂eq/t</t>
+          <t>million heads</t>
         </is>
       </c>
       <c r="E35" s="13" t="n">
         <v>2020</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1.264</v>
+        <v>20.63</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>1.238</v>
+        <v>19.02</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>-0.02600000000000002</v>
+        <v>-1.609999999999999</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>-0.02056962025316458</v>
+        <v>-0.07804168686379057</v>
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
@@ -3192,19 +3468,19 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>L8</t>
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>O2 (FEC)</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Total bioenergy use (EU-27)</t>
+          <t>Final energy consumption (EU-27)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>LULUCF</t>
+          <t>Energy demand</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -3216,19 +3492,19 @@
         <v>2021</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1795.7</v>
+        <v>11263</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1761.2</v>
+        <v>10471.8</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>-34.5</v>
+        <v>-791.2000000000007</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.01921256334577045</v>
+        <v>-0.0702477137529966</v>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
@@ -3237,133 +3513,133 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>A6</t>
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>I4 (cement)</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Food waste per capita (EU)</t>
+          <t>GHG intensity of EU cement production</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>t CO₂eq/t</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.6038</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>-0.04239999999999999</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>-0.07022192779065915</v>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>A4 (bovine, herd)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Bovine meat: herd size (EU)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>kg/cap/year</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="n">
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>million heads</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="F37" s="14" t="n">
-        <v>131</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <v>129</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J37" s="15" t="n">
-        <v>-0.01526717557251908</v>
-      </c>
-      <c r="K37" s="16" t="inlineStr">
+      <c r="F38" s="8" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>-3.899999999999999</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>-0.06482712765957445</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>Reproduces from source</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Agricultural non-CO₂ emissions</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>A2 (pig, production)</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Pig meat: production (EU)</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>360.9</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>355.7</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>-5.199999999999989</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>-0.01440842338597947</v>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="29" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>EU R&amp;D expenditure (GERD)</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Finance &amp; innovation</t>
-        </is>
-      </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>% of GDP</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>2.27</v>
+        <v>23.22</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>2.24</v>
+        <v>21.84</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>-0.0299999999999998</v>
+        <v>-1.379999999999999</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>-0.01321585903083692</v>
+        <v>-0.05943152454780358</v>
       </c>
       <c r="K39" s="16" t="inlineStr">
         <is>
@@ -3374,102 +3650,102 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="27" t="inlineStr">
         <is>
-          <t>T6a</t>
+          <t>A4 (pig, production)</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Fossil share of transport energy use</t>
+          <t>Pig meat: production (EU)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>-1.379999999999999</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>-0.05943152454780358</v>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>I4 (steel)</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>GHG intensity of EU steel production</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>t CO₂eq/t</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n">
         <v>2021</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>93.17</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>-0.269999999999996</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>-0.002889554794520505</v>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>A2 (dairy, production)</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Dairy products: production (EU)</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>2020</v>
-      </c>
       <c r="F41" s="14" t="n">
-        <v>163.1</v>
+        <v>0.9623</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>164.6</v>
+        <v>0.911</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.5</v>
+        <v>-0.05130000000000001</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0.009196811771919068</v>
+        <v>-0.05330977865530501</v>
       </c>
       <c r="K41" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>A4 (dairy, production)</t>
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>A2 (dairy, intensity)</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Dairy products: production (EU)</t>
+          <t>Dairy products: GHG intensity (EU)</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -3479,341 +3755,341 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>t CO₂eq/t</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>163.1</v>
+        <v>0.6049</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>164.6</v>
+        <v>0.5728</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>1.5</v>
+        <v>-0.03210000000000002</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.009196811771919068</v>
+        <v>-0.05306662258224503</v>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
-        <is>
-          <t>B4 (population)</t>
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>A5 (bovine)</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>EU population (index, 2005 = 1.0)</t>
+          <t>Average bovine meat consumption (EU)</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>index (2005 = 1.0)</t>
+          <t>kcal/cap/day</t>
         </is>
       </c>
       <c r="E43" s="13" t="n">
         <v>2020</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>1.028</v>
+        <v>52.12</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>1.04</v>
+        <v>49.48</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.01200000000000001</v>
+        <v>-2.640000000000001</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0.01167315175097277</v>
+        <v>-0.05065234075211053</v>
       </c>
       <c r="K43" s="16" t="inlineStr">
         <is>
-          <t>Reproduces from source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>A4 (bovine, consumption)</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Transport GHG emissions (EU)</t>
+          <t>Bovine meat: consumption (EU)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>6.115</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>-0.2480000000000002</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>-0.04055600981193788</v>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>T3a</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Road share of motorised inland passenger transport</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>906.6</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>920</v>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>13.39999999999998</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>0.01478049856607101</v>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>F2 (share)</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Green share of EU bond issuance</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Finance &amp; innovation</t>
-        </is>
-      </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
       <c r="E45" s="13" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>6.74</v>
+        <v>86.5</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>6.9</v>
+        <v>83.3</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.1600000000000001</v>
+        <v>-3.200000000000003</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0.02373887240356085</v>
+        <v>-0.03699421965317922</v>
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>I6</t>
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>A2 (bovine, GHG)</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Electricity share of industrial final energy use</t>
+          <t>Bovine meat: GHG emissions (EU)</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>33.22</v>
+        <v>100.3</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>34.02</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.8000000000000043</v>
+        <v>-3.480000000000004</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.02408187838651428</v>
+        <v>-0.03469591226321041</v>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>2–5% off source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
-        <is>
-          <t>T2b</t>
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>A2 (dairy, GHG)</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Total freight transport demand</t>
+          <t>Dairy products: GHG emissions (EU)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Gtkm</t>
+          <t>Mt CO₂eq</t>
         </is>
       </c>
       <c r="E47" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>-3.220000000000013</v>
+      </c>
+      <c r="J47" s="15" t="n">
+        <v>-0.03292770221904093</v>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>A2 (pig, intensity)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Pig meat: GHG intensity (EU)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>t CO₂eq/t</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="F47" s="14" t="n">
-        <v>2254</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H47" s="14" t="n">
-        <v>2319</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>65</v>
-      </c>
-      <c r="J47" s="15" t="n">
-        <v>0.02883762200532387</v>
-      </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Electrification rate of final energy use</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Energy demand</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>2021</v>
-      </c>
       <c r="F48" s="8" t="n">
-        <v>22.75</v>
+        <v>1.264</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>23.44</v>
+        <v>1.238</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.6900000000000013</v>
+        <v>-0.02600000000000002</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.03032967032967039</v>
+        <v>-0.02056962025316458</v>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>I3</t>
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Circular material use rate (EU)</t>
+          <t>Total bioenergy use (EU-27)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>LULUCF</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>TWh</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
         <v>2021</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>11.7</v>
+        <v>1795.7</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>12.2</v>
+        <v>1761.2</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.5</v>
+        <v>-34.5</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0.04273504273504274</v>
+        <v>-0.01921256334577045</v>
       </c>
       <c r="K49" s="16" t="inlineStr">
         <is>
@@ -3822,88 +4098,88 @@
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>L1</t>
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>A6</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>LULUCF net GHG balance</t>
+          <t>Food waste per capita (EU)</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>LULUCF</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
+          <t>kg/cap/year</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>-0.01526717557251908</v>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Agricultural non-CO₂ emissions</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
           <t>Mt CO₂eq</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E51" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>-244</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>-231</v>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>0.05327868852459016</v>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>Reproduces from source</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>Forest land living-biomass carbon sink</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>LULUCF</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>Mt CO₂eq</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>2021</v>
-      </c>
       <c r="F51" s="14" t="n">
-        <v>231.8</v>
+        <v>360.9</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>258.3</v>
+        <v>355.7</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>26.5</v>
+        <v>-5.199999999999989</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0.1143226919758412</v>
+        <v>-0.01440842338597947</v>
       </c>
       <c r="K51" s="16" t="inlineStr">
         <is>
@@ -3912,43 +4188,43 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>L7</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>F3</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Non-forest LULUCF net GHG emissions</t>
+          <t>EU R&amp;D expenditure (GERD)</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>LULUCF</t>
+          <t>Finance &amp; innovation</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Mt CO₂eq</t>
+          <t>% of GDP</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>97.44</v>
+        <v>2.27</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>123</v>
+        <v>2.24</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>25.56</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.2623152709359606</v>
+        <v>-0.01321585903083692</v>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
@@ -3957,544 +4233,1579 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>E2 (RES)</t>
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>A5 (pig)</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Non-biomass renewable share of EU electricity mix</t>
+          <t>Average pig meat consumption (EU)</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Energy supply</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kcal/cap/day</t>
         </is>
       </c>
       <c r="E53" s="13" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>33.76</v>
+        <v>203.8</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>43.21</v>
+        <v>201.99</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>9.450000000000003</v>
+        <v>-1.810000000000002</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.2799170616113745</v>
+        <v>-0.008881256133464192</v>
       </c>
       <c r="K53" s="16" t="inlineStr">
         <is>
-          <t>2–5% off source</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>B6</t>
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>A2 (bovine, intensity)</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>EU stock of installed heat pumps</t>
+          <t>Bovine meat: GHG intensity (EU)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>million units</t>
+          <t>t CO₂eq/t</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>19.79</v>
+        <v>14.53</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>25.5</v>
+        <v>14.447</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>5.710000000000001</v>
+        <v>-0.08300000000000018</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.2885295603840324</v>
+        <v>-0.005712319339298017</v>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>T5a</t>
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>A4 (pig, consumption)</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>ZEV share of new passenger car registrations</t>
+          <t>Pig meat: consumption (EU)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>17.397</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>-0.06300000000000239</v>
+      </c>
+      <c r="J55" s="15" t="n">
+        <v>-0.003608247422680549</v>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>T6a</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Fossil share of transport energy use</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E55" s="13" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H55" s="14" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>3.989999999999998</v>
-      </c>
-      <c r="J55" s="15" t="n">
-        <v>0.2975391498881431</v>
-      </c>
-      <c r="K55" s="16" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>T2a</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Total passenger transport demand</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Gpkm</t>
-        </is>
-      </c>
       <c r="E56" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>93.17</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>-0.269999999999996</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>-0.002889554794520505</v>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>A2 (dairy, production)</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Dairy products: production (EU)</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="n">
         <v>2020</v>
       </c>
-      <c r="F56" s="8" t="n">
-        <v>4435.8</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>5932</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>1496.2</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>0.3373010505433067</v>
-      </c>
-      <c r="K56" s="10" t="inlineStr">
-        <is>
-          <t>Published figure, not re-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="18" t="inlineStr">
-        <is>
-          <t>E4b/c</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>Annual wind capacity additions (EU)</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>Energy supply</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>GW/yr</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>2021</v>
-      </c>
       <c r="F57" s="14" t="n">
-        <v>10.72</v>
+        <v>163.1</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>15.32</v>
+        <v>164.6</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>0.4291044776119403</v>
+        <v>0.009196811771919068</v>
       </c>
       <c r="K57" s="16" t="inlineStr">
         <is>
-          <t>Published figure, not re-derived</t>
+          <t>Reproduces from source</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>E4a</t>
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>A4 (dairy, production)</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Annual solar PV capacity additions (EU)</t>
+          <t>Dairy products: production (EU)</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Energy supply</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>GW/yr</t>
+          <t>Mt</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>25.7</v>
+        <v>163.1</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H58" s="8" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.009196811771919068</v>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>B4 (population)</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>EU population (index, 2005 = 1.0)</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>index (2005 = 1.0)</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="J59" s="15" t="n">
+        <v>0.01167315175097277</v>
+      </c>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Transport GHG emissions (EU)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Mt CO₂eq</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>906.6</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>920</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>13.39999999999998</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.01478049856607101</v>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>F2 (share)</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Green share of EU bond issuance</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Finance &amp; innovation</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="J61" s="15" t="n">
+        <v>0.02373887240356085</v>
+      </c>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Electricity share of industrial final energy use</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>0.8000000000000043</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.02408187838651428</v>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>2–5% off source</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Agricultural products used as bioenergy feedstock</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Mt fresh</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>0.620000000000001</v>
+      </c>
+      <c r="J63" s="15" t="n">
+        <v>0.0259522812892424</v>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>T2b</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Total freight transport demand</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Gtkm</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>2254</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>2319</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.02883762200532387</v>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Electrification rate of final energy use</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Energy demand</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H65" s="14" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>0.6900000000000013</v>
+      </c>
+      <c r="J65" s="15" t="n">
+        <v>0.03032967032967039</v>
+      </c>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>A5 (dairy)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Average dairy products consumption (EU)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>kcal/cap/day</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>550.4</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>569.13</v>
+      </c>
+      <c r="I66" s="8" t="n">
+        <v>18.73000000000002</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0.03402979651162794</v>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Circular material use rate (EU)</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J67" s="15" t="n">
+        <v>0.04273504273504274</v>
+      </c>
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>A4 (dairy, consumption)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Dairy products: consumption (EU)</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>91.16200000000001</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>4.532000000000011</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.05231444072492221</v>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>LULUCF net GHG balance</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>LULUCF</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Mt CO₂eq</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>-244</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H69" s="14" t="n">
+        <v>-231</v>
+      </c>
+      <c r="I69" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J69" s="15" t="n">
+        <v>0.05327868852459016</v>
+      </c>
+      <c r="K69" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Forest land living-biomass carbon sink</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>LULUCF</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Mt CO₂eq</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>231.8</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0.1143226919758412</v>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>I7a</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Low-carbon steel projects (EU)</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H71" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="I71" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J71" s="15" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="K71" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>I7c</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Low-carbon chemicals projects (EU)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.2573099415204678</v>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Non-forest LULUCF net GHG emissions</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>LULUCF</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Mt CO₂eq</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>97.44</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="I73" s="14" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <v>0.2623152709359606</v>
+      </c>
+      <c r="K73" s="16" t="inlineStr">
+        <is>
+          <t>Reproduces from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>E2 (RES)</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Non-biomass renewable share of EU electricity mix</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Energy supply</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>9.450000000000003</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>0.2799170616113745</v>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>2–5% off source</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>EU stock of installed heat pumps</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>million units</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I75" s="14" t="n">
+        <v>5.710000000000001</v>
+      </c>
+      <c r="J75" s="15" t="n">
+        <v>0.2885295603840324</v>
+      </c>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>T5a</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>ZEV share of new passenger car registrations</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>3.989999999999998</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.2975391498881431</v>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>T2a</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Total passenger transport demand</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Gpkm</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>4435.8</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>5932</v>
+      </c>
+      <c r="I77" s="14" t="n">
+        <v>1496.2</v>
+      </c>
+      <c r="J77" s="15" t="n">
+        <v>0.3373010505433067</v>
+      </c>
+      <c r="K77" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>I2 (chemicals, trade)</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Chemicals net trade balance (EU)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>-2.268</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>-1.357</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>0.9109999999999998</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0.4016754850088183</v>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>E4b/c</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Annual wind capacity additions (EU)</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Energy supply</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>GW/yr</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="I79" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J79" s="15" t="n">
+        <v>0.4291044776119403</v>
+      </c>
+      <c r="K79" s="16" t="inlineStr">
+        <is>
+          <t>Published figure, not re-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>I7b</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Low-carbon cement projects (EU)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>E4a</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Annual solar PV capacity additions (EU)</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Energy supply</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>GW/yr</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H81" s="14" t="n">
         <v>60.96</v>
       </c>
-      <c r="I58" s="8" t="n">
+      <c r="I81" s="14" t="n">
         <v>35.26000000000001</v>
       </c>
-      <c r="J58" s="9" t="n">
+      <c r="J81" s="15" t="n">
         <v>1.371984435797665</v>
       </c>
-      <c r="K58" s="10" t="inlineStr">
+      <c r="K81" s="16" t="inlineStr">
         <is>
           <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="21" t="inlineStr">
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
         <is>
           <t>T5b</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Zero-emission lorries in the EU fleet</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E82" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="F59" s="14" t="n">
+      <c r="F82" s="8" t="n">
         <v>3794</v>
       </c>
-      <c r="G59" s="13" t="n">
+      <c r="G82" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="H59" s="14" t="n">
+      <c r="H82" s="8" t="n">
         <v>9831</v>
       </c>
-      <c r="I59" s="14" t="n">
+      <c r="I82" s="8" t="n">
         <v>6037</v>
       </c>
-      <c r="J59" s="15" t="n">
+      <c r="J82" s="9" t="n">
         <v>1.591196626251977</v>
       </c>
-      <c r="K59" s="16" t="inlineStr">
+      <c r="K82" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="22" t="inlineStr">
         <is>
           <t>T3b</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>Intra-EU air passenger transport</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C83" s="12" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>Gpkm</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E83" s="13" t="n">
         <v>2020</v>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F83" s="14" t="n">
         <v>177.9</v>
       </c>
-      <c r="G60" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H60" s="8" t="n">
-        <v>582</v>
-      </c>
-      <c r="I60" s="8" t="n">
-        <v>404.1</v>
-      </c>
-      <c r="J60" s="9" t="n">
-        <v>2.27150084317032</v>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
+      <c r="G83" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>637.8</v>
+      </c>
+      <c r="I83" s="14" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="J83" s="15" t="n">
+        <v>2.585160202360877</v>
+      </c>
+      <c r="K83" s="16" t="inlineStr">
         <is>
           <t>Published figure, not re-derived</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="32" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="32" t="inlineStr">
         <is>
           <t>Notes: bars are coloured by report chapter. A long bar is a large move relative to that indicator's own baseline, not a large quantity — indicators with small baselines (capacity additions, ZEV shares) move by large percentages by nature.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="32" t="inlineStr">
-        <is>
-          <t>Source: ESABCC (2024) “Towards EU climate neutrality”, progress indicators, extended with the post-publication points in the Policy Gap 2.0 indicator database. Every post-report value was re-checked against its primary source on 27 July 2026 (see the “Source check” column).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="33" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>Source: ESABCC (2024) “Towards EU climate neutrality”, progress indicators, extended with the post-publication points in the Policy Gap 2.0 indicator database. The “Source check” column carries the 27 July 2026 fact-check, which covers 52 of these 78 indicators; series refreshed since that check show “—” rather than a verdict, and have not been re-checked against their source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="33" t="inlineStr">
         <is>
           <t>Coverage — how much of each chapter has new data</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="4" t="inlineStr"/>
-      <c r="B66" s="4" t="inlineStr">
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="4" t="inlineStr"/>
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Chapter</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>With new data</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Still at the report figure</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="6" t="inlineStr"/>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Emissions</t>
         </is>
       </c>
-      <c r="C67" s="34" t="n">
+      <c r="C90" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="34" t="n">
+      <c r="D90" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="12" t="inlineStr"/>
-      <c r="B68" s="12" t="inlineStr">
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="12" t="inlineStr"/>
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>Energy supply</t>
         </is>
       </c>
-      <c r="C68" s="35" t="n">
+      <c r="C91" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="D68" s="35" t="n">
+      <c r="D91" s="35" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="6" t="inlineStr">
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="6" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Energy demand</t>
         </is>
       </c>
-      <c r="C69" s="34" t="n">
+      <c r="C92" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D69" s="34" t="n">
+      <c r="D92" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="12" t="inlineStr"/>
-      <c r="B70" s="12" t="inlineStr">
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="12" t="inlineStr"/>
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="C70" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="D70" s="35" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="6" t="inlineStr"/>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="C93" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="D93" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="6" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="C71" s="34" t="n">
+      <c r="C94" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="12" t="inlineStr"/>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="C95" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D95" s="35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="6" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="C96" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D96" s="34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="12" t="inlineStr"/>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>LULUCF</t>
+        </is>
+      </c>
+      <c r="C97" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="D71" s="34" t="n">
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="6" t="inlineStr"/>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Finance &amp; innovation</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" s="34" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="12" t="inlineStr"/>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>Buildings</t>
-        </is>
-      </c>
-      <c r="C72" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" s="35" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="6" t="inlineStr"/>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C73" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="D73" s="34" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="12" t="inlineStr"/>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>LULUCF</t>
-        </is>
-      </c>
-      <c r="C74" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D74" s="35" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="6" t="inlineStr"/>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Finance &amp; innovation</t>
-        </is>
-      </c>
-      <c r="C75" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D75" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:K60"/>
+  <autoFilter ref="A5:K83"/>
   <mergeCells count="5">
-    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A86:K86"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="A85:K85"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
+++ b/project-documents/summer-prep-background/ESABCC_Indicator-New-Data-Overview_2026-07.xlsx
@@ -368,6 +368,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1358,6 +1359,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
@@ -1479,6 +1481,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1609,6 +1612,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
